--- a/artfynd/A 896-2025 artfynd.xlsx
+++ b/artfynd/A 896-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103554290</v>
+        <v>103554279</v>
       </c>
       <c r="B2" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>614188.5241104666</v>
+        <v>613948</v>
       </c>
       <c r="R2" t="n">
-        <v>7179526.758846895</v>
+        <v>7179296</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2022-08-24</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-08-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103554285</v>
+        <v>103554281</v>
       </c>
       <c r="B3" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>614142.1750047932</v>
+        <v>613949</v>
       </c>
       <c r="R3" t="n">
-        <v>7179257.142211878</v>
+        <v>7179294</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,19 +844,9 @@
           <t>2022-08-24</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-08-24</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,12 +880,7 @@
         <v>103554282</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>614113.1958149679</v>
+        <v>614113</v>
       </c>
       <c r="R4" t="n">
-        <v>7179253.050631692</v>
+        <v>7179253</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,19 +945,9 @@
           <t>2022-08-24</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-08-24</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103554288</v>
+        <v>103554284</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>614245.2357940335</v>
+        <v>614142</v>
       </c>
       <c r="R5" t="n">
-        <v>7179420.651047518</v>
+        <v>7179257</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,19 +1046,9 @@
           <t>2022-08-24</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-08-24</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103554289</v>
+        <v>103554285</v>
       </c>
       <c r="B6" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1155,39 +1090,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Isnottjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>614188.6696610647</v>
+        <v>614142</v>
       </c>
       <c r="R6" t="n">
-        <v>7179522.913460471</v>
+        <v>7179257</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,19 +1147,9 @@
           <t>2022-08-24</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-08-24</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,37 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103554283</v>
+        <v>103554288</v>
       </c>
       <c r="B7" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>614142.1750047932</v>
+        <v>614245</v>
       </c>
       <c r="R7" t="n">
-        <v>7179257.142211878</v>
+        <v>7179420</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,19 +1248,9 @@
           <t>2022-08-24</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-08-24</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1379,12 +1284,7 @@
         <v>103554287</v>
       </c>
       <c r="B8" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1421,10 +1321,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>614245.2357940335</v>
+        <v>614245</v>
       </c>
       <c r="R8" t="n">
-        <v>7179420.651047518</v>
+        <v>7179420</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1454,19 +1354,9 @@
           <t>2022-08-24</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-08-24</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1497,15 +1387,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>103554284</v>
+        <v>103554289</v>
       </c>
       <c r="B9" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1513,34 +1398,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Isnottjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>614142.1750047932</v>
+        <v>614189</v>
       </c>
       <c r="R9" t="n">
-        <v>7179257.142211878</v>
+        <v>7179523</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1570,19 +1460,9 @@
           <t>2022-08-24</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-08-24</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
